--- a/out/MLP-Mamba1_repeat_5_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7499999781250002</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7499999781250002</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.166666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.566666627777778</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.566666627777778</v>
+        <v>1.279412977671564</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.566666627777778</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.166666627777778</v>
+        <v>-0.9409673395990859</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.166666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.566666627777778</v>
+        <v>1.879412977671564</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>-1.540967339599086</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.566666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.566666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.5599999850000003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.5599999850000003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7499999781250002</v>
+        <v>-0.5599999850000003</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.5599999850000003</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.166666627777778</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.349999978125</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.566666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.349999978125</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.166666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.566666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.349999978125</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.566666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.1066666677777778</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.166666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.566666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.166666627777778</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7499999781250002</v>
+        <v>0.7733333205555558</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.566666627777778</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.349999978125</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.349999978125</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.566666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.166666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.566666627777778</v>
+        <v>1.439999973333334</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.566666627777778</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.566666627777778</v>
+        <v>1.239999973333334</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.566666627777778</v>
+        <v>0.5733333205555557</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.09333333222222223</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.349999978125</v>
+        <v>-0.7599999850000003</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4781228601932526</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.02000000000000018</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4783914685249329</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.1600000000000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5158455967903137</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4741812646389008</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4399658143520355</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4670740067958832</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.5142868757247925</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3857003152370453</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4187674820423126</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3869469463825226</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4500788450241089</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3894295990467072</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4098359048366547</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3887118995189667</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3928828239440918</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5346896052360535</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4964237213134766</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.6037779450416565</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4503230154514313</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5897508263587952</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4531919360160828</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1066666677777778</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3676182925701141</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3873439133167267</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4929751455783844</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.422968327999115</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3675695657730103</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4729005992412567</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3866557478904724</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3986001014709473</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4469723105430603</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.6581391096115112</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.430002361536026</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3516902327537537</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5599999850000003</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4426244497299194</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5599999850000003</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3794772028923035</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.3153626918792725</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4760433733463287</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4301886558532715</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.3485717475414276</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4420563578605652</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.3997478485107422</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.393325537443161</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.3683993816375732</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3606537878513336</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4216454327106476</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3728955686092377</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3984323441982269</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3653550744056702</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3616927862167358</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3861086070537567</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4546168744564056</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4112312197685242</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.3</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3589478731155396</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4509052932262421</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7599999850000003</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3447869122028351</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.5231147408485413</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3536209166049957</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4483353793621063</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5599999850000003</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4386827051639557</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3453240692615509</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3456029891967773</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3688037693500519</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3718551099300385</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3645310699939728</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3573985993862152</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4087717533111572</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3577613532543182</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.349926084280014</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3789210915565491</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3303043842315674</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2517266273498535</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2942884564399719</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.6142879128456116</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4530026018619537</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.5950624346733093</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.632396399974823</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5869611501693726</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4922333359718323</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4828366041183472</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5326655507087708</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.09333333222222223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4437460899353027</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5733333205555557</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6202203631401062</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5733333205555557</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5380845069885254</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.439999973333334</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.626761257648468</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.5062695145606995</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.6045207381248474</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.439999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.6111215949058533</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5991927981376648</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4036873281002045</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4379362165927887</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5201083421707153</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.4720757305622101</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6052622199058533</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5733333205555557</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.5466303825378418</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.439999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6578956842422485</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.4688248932361603</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1066666677777778</v>
+        <v>0.3</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.489485114812851</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5261840224266052</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5315282344818115</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.4343222677707672</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6876844167709351</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7733333205555558</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5011527538299561</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.439999973333334</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5566044449806213</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.439999973333334</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.598518431186676</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4838925898075104</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7733333205555558</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.5519246459007263</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4822187125682831</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5135603547096252</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.5313231348991394</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4847762584686279</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5157764554023743</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.5303053855895996</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.439999973333334</v>
+        <v>0.3</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6028837561607361</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.439999973333334</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.5827029347419739</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.6339303851127625</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.6593426465988159</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.6226100921630859</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.439999973333334</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.6909663081169128</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.6065894365310669</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5834744572639465</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.439999973333334</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.6679385900497437</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.239999973333334</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.7118195295333862</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.239999973333334</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.6171330213546753</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5733333205555557</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4650518000125885</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.09333333222222223</v>
+        <v>-0.7200000000000006</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4398910105228424</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7599999850000003</v>
+        <v>-1.140000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_5_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000005.xlsx
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.5142868757247925</v>
+        <v>0.5142869353294373</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.3857003152370453</v>
+        <v>0.3857003748416901</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4187674820423126</v>
+        <v>0.4187675714492798</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3869469463825226</v>
+        <v>0.386946976184845</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4500788450241089</v>
+        <v>0.4500788748264313</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3894295990467072</v>
+        <v>0.3894296586513519</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.4098359048366547</v>
+        <v>0.4098359644412994</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3887118995189667</v>
+        <v>0.3887119293212891</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.3928828239440918</v>
+        <v>0.3928828835487366</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.6037779450416565</v>
+        <v>0.6037778258323669</v>
       </c>
       <c r="JB19" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.5897508263587952</v>
+        <v>0.5897507667541504</v>
       </c>
       <c r="JB21" t="n">
         <v>0.1600000000000001</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.4531919360160828</v>
+        <v>0.453191876411438</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.1199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.3676182925701141</v>
+        <v>0.3676183223724365</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3873439133167267</v>
+        <v>0.3873439431190491</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4929751455783844</v>
+        <v>0.4929752051830292</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.422968327999115</v>
+        <v>0.4229683578014374</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.3675695657730103</v>
+        <v>0.367569625377655</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4729005992412567</v>
+        <v>0.4729006588459015</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.3866557478904724</v>
+        <v>0.3866558372974396</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3986001014709473</v>
+        <v>0.3986001908779144</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4469723105430603</v>
+        <v>0.4469723999500275</v>
       </c>
       <c r="JB31" t="n">
         <v>0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.6581391096115112</v>
+        <v>0.658139169216156</v>
       </c>
       <c r="JB32" t="n">
         <v>0.02000000000000007</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3794772028923035</v>
+        <v>0.3794772922992706</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.3153626918792725</v>
+        <v>0.3153627216815948</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4760433733463287</v>
+        <v>0.4760434329509735</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.3485717475414276</v>
+        <v>0.34857177734375</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.4420563578605652</v>
+        <v>0.4420563876628876</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.3997478485107422</v>
+        <v>0.3997478783130646</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.393325537443161</v>
+        <v>0.3933256268501282</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.3683993816375732</v>
+        <v>0.368399441242218</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.3606537878513336</v>
+        <v>0.3606538772583008</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.4216454327106476</v>
+        <v>0.42164546251297</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.3728955686092377</v>
+        <v>0.3728956282138824</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.3984323441982269</v>
+        <v>0.3984323740005493</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.3653550744056702</v>
+        <v>0.3653551340103149</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3616927862167358</v>
+        <v>0.361692875623703</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.1199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3861086070537567</v>
+        <v>0.3861086666584015</v>
       </c>
       <c r="JB51" t="n">
         <v>0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.4546168744564056</v>
+        <v>0.4546169340610504</v>
       </c>
       <c r="JB52" t="n">
         <v>0.02000000000000007</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4112312197685242</v>
+        <v>0.4112312793731689</v>
       </c>
       <c r="JB53" t="n">
         <v>0.3</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.3589478731155396</v>
+        <v>0.3589479625225067</v>
       </c>
       <c r="JB54" t="n">
         <v>0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.4509052932262421</v>
+        <v>0.4509053528308868</v>
       </c>
       <c r="JB55" t="n">
         <v>0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.3447869122028351</v>
+        <v>0.3447869420051575</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3536209166049957</v>
+        <v>0.3536209464073181</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.3453240692615509</v>
+        <v>0.3453241288661957</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.3456029891967773</v>
+        <v>0.3456030189990997</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3688037693500519</v>
+        <v>0.3688038885593414</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3718551099300385</v>
+        <v>0.3718551695346832</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3645310699939728</v>
+        <v>0.3645311594009399</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.3573985993862152</v>
+        <v>0.3573987185955048</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.4087717533111572</v>
+        <v>0.4087718427181244</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3577613532543182</v>
+        <v>0.357761412858963</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.349926084280014</v>
+        <v>0.3499261736869812</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3789210915565491</v>
+        <v>0.3789211511611938</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.3303043842315674</v>
+        <v>0.3303044736385345</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2517266273498535</v>
+        <v>0.2517267167568207</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2942884564399719</v>
+        <v>0.2942885160446167</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.6142879128456116</v>
+        <v>0.6142877340316772</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4530026018619537</v>
+        <v>0.4530025124549866</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.5950624346733093</v>
+        <v>0.5950628519058228</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.632396399974823</v>
+        <v>0.6323962211608887</v>
       </c>
       <c r="JB77" t="n">
         <v>0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5869611501693726</v>
+        <v>0.5869609117507935</v>
       </c>
       <c r="JB78" t="n">
         <v>0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.4922333359718323</v>
+        <v>0.4922332763671875</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4437460899353027</v>
+        <v>0.4437460005283356</v>
       </c>
       <c r="JB82" t="n">
         <v>0.1199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6202203631401062</v>
+        <v>0.6202202439308167</v>
       </c>
       <c r="JB83" t="n">
         <v>0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.5380845069885254</v>
+        <v>0.5380843877792358</v>
       </c>
       <c r="JB84" t="n">
         <v>0.1199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.626761257648468</v>
+        <v>0.6267611980438232</v>
       </c>
       <c r="JB85" t="n">
         <v>0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.6111215949058533</v>
+        <v>0.6111214160919189</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.16</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.5991927981376648</v>
+        <v>0.5991926789283752</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.4036873281002045</v>
+        <v>0.4036872386932373</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5201083421707153</v>
+        <v>0.5201082825660706</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.4720757305622101</v>
+        <v>0.4720756709575653</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.6052622199058533</v>
+        <v>0.6052621603012085</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1199999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.5466303825378418</v>
+        <v>0.5466302633285522</v>
       </c>
       <c r="JB95" t="n">
         <v>0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6578956842422485</v>
+        <v>0.657895565032959</v>
       </c>
       <c r="JB96" t="n">
         <v>0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.4688248932361603</v>
+        <v>0.4688248336315155</v>
       </c>
       <c r="JB97" t="n">
         <v>0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.5261840224266052</v>
+        <v>0.5261839628219604</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.4343222677707672</v>
+        <v>0.4343221783638</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.6876844167709351</v>
+        <v>0.6876842379570007</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.3</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.5011527538299561</v>
+        <v>0.5011526942253113</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1600000000000001</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.5566044449806213</v>
+        <v>0.5566043853759766</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.598518431186676</v>
+        <v>0.5985183119773865</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4838925898075104</v>
+        <v>0.483892410993576</v>
       </c>
       <c r="JB106" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.4822187125682831</v>
+        <v>0.4822185933589935</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5135603547096252</v>
+        <v>0.5135602951049805</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.5313231348991394</v>
+        <v>0.5313230752944946</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.5303053855895996</v>
+        <v>0.5303053259849548</v>
       </c>
       <c r="JB113" t="n">
         <v>0.3</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.6028837561607361</v>
+        <v>0.6028843522071838</v>
       </c>
       <c r="JB114" t="n">
         <v>0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.5827029347419739</v>
+        <v>0.5827028155326843</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.6339303851127625</v>
+        <v>0.633931040763855</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.6593426465988159</v>
+        <v>0.6593422293663025</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.6226100921630859</v>
+        <v>0.6226107478141785</v>
       </c>
       <c r="JB118" t="n">
         <v>0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.6909663081169128</v>
+        <v>0.6909659504890442</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.6679385900497437</v>
+        <v>0.6679390668869019</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.7118195295333862</v>
+        <v>0.7118191719055176</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.6171330213546753</v>
+        <v>0.617133617401123</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4650518000125885</v>
+        <v>0.465051680803299</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7200000000000006</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4398910105228424</v>
+        <v>0.4398910403251648</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.140000000000001</v>
